--- a/推荐订单占比 (21).xlsx
+++ b/推荐订单占比 (21).xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\jiangziyi\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\jiangziyi\Downloads\car-owner-dashboard-github-auto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47BA0FC5-AB57-4DCA-A2C3-5F94B7795530}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{126C1392-3C9E-4204-BC52-B698E6ECEC1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,8 +33,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="28">
   <si>
     <t>锁单区域部门名称</t>
   </si>
@@ -124,11 +146,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="176" formatCode="###,###,###,###,###,##0"/>
     <numFmt numFmtId="177" formatCode="###,###,###,###,###,##0.0%"/>
+    <numFmt numFmtId="178" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -207,8 +230,29 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -235,8 +279,23 @@
         <fgColor rgb="FFF3F3F6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7EDED"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3F6F6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAEC2C2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -259,13 +318,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF698E8E"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF698E8E"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF698E8E"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF698E8E"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -296,11 +373,85 @@
     <xf numFmtId="176" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="百分比" xfId="1" builtinId="5"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -610,15 +761,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="3" width="38" customWidth="1"/>
     <col min="4" max="4" width="41" customWidth="1"/>
+    <col min="5" max="5" width="27.08203125" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="0" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="25" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="32" customHeight="1">
+    <row r="1" spans="1:7" ht="32" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -632,7 +786,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="32" customHeight="1">
+    <row r="2" spans="1:7" ht="32" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -642,14 +796,14 @@
       </c>
       <c r="C2" s="3">
         <f>SUM(C3:C25)</f>
-        <v>10433</v>
+        <v>8459</v>
       </c>
       <c r="D2" s="4">
         <f>C2/B2</f>
-        <v>0.28507801185889553</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="32" customHeight="1">
+        <v>0.23113916441238352</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="32" customHeight="1">
       <c r="A3" s="6" t="s">
         <v>5</v>
       </c>
@@ -657,14 +811,25 @@
         <v>1633</v>
       </c>
       <c r="C3" s="7">
-        <v>563</v>
+        <v>425</v>
       </c>
       <c r="D3" s="8">
         <f>C3/B3</f>
-        <v>0.34476423759951008</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="32" customHeight="1">
+        <v>0.26025719534598896</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" cm="1">
+        <f t="array" ref="F3:F25">VLOOKUP(E3:E25,A3:D25,3,FALSE)</f>
+        <v>425</v>
+      </c>
+      <c r="G3" s="13" cm="1">
+        <f t="array" ref="G3:G25">VLOOKUP(E3:E25,A3:D25,4,FALSE)</f>
+        <v>0.26025719534598896</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="32" customHeight="1">
       <c r="A4" s="5" t="s">
         <v>6</v>
       </c>
@@ -672,14 +837,23 @@
         <v>718</v>
       </c>
       <c r="C4" s="9">
-        <v>237</v>
+        <v>197</v>
       </c>
       <c r="D4" s="8">
         <f t="shared" ref="D4:D25" si="0">C4/B4</f>
-        <v>0.33008356545961004</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="32" customHeight="1">
+        <v>0.27437325905292481</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4">
+        <v>124</v>
+      </c>
+      <c r="G4" s="13">
+        <v>0.18049490538573509</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="32" customHeight="1">
       <c r="A5" s="6" t="s">
         <v>7</v>
       </c>
@@ -687,14 +861,23 @@
         <v>4708</v>
       </c>
       <c r="C5" s="7">
-        <v>1526</v>
+        <v>1235</v>
       </c>
       <c r="D5" s="8">
         <f t="shared" si="0"/>
-        <v>0.32412914188615122</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="32" customHeight="1">
+        <v>0.26231945624468989</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5">
+        <v>379</v>
+      </c>
+      <c r="G5" s="13">
+        <v>0.21256309590577679</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="32" customHeight="1">
       <c r="A6" s="5" t="s">
         <v>8</v>
       </c>
@@ -702,14 +885,23 @@
         <v>1418</v>
       </c>
       <c r="C6" s="9">
-        <v>450</v>
+        <v>382</v>
       </c>
       <c r="D6" s="8">
         <f t="shared" si="0"/>
-        <v>0.31734837799717913</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="32" customHeight="1">
+        <v>0.26939351198871653</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6">
+        <v>477</v>
+      </c>
+      <c r="G6" s="13">
+        <v>0.22757633587786261</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="32" customHeight="1">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
@@ -717,14 +909,23 @@
         <v>1356</v>
       </c>
       <c r="C7" s="7">
-        <v>422</v>
+        <v>356</v>
       </c>
       <c r="D7" s="8">
         <f t="shared" si="0"/>
-        <v>0.3112094395280236</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="32" customHeight="1">
+        <v>0.26253687315634217</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7">
+        <v>137</v>
+      </c>
+      <c r="G7" s="13">
+        <v>0.18870523415977961</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="32" customHeight="1">
       <c r="A8" s="5" t="s">
         <v>10</v>
       </c>
@@ -732,14 +933,23 @@
         <v>1883</v>
       </c>
       <c r="C8" s="9">
-        <v>576</v>
+        <v>498</v>
       </c>
       <c r="D8" s="8">
         <f t="shared" si="0"/>
-        <v>0.30589484864577804</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="32" customHeight="1">
+        <v>0.26447158789166225</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8">
+        <v>240</v>
+      </c>
+      <c r="G8" s="13">
+        <v>0.24291497975708501</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="32" customHeight="1">
       <c r="A9" s="6" t="s">
         <v>11</v>
       </c>
@@ -747,14 +957,23 @@
         <v>1327</v>
       </c>
       <c r="C9" s="7">
-        <v>403</v>
+        <v>328</v>
       </c>
       <c r="D9" s="8">
         <f t="shared" si="0"/>
-        <v>0.30369253956292391</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="32" customHeight="1">
+        <v>0.24717407686510928</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9">
+        <v>617</v>
+      </c>
+      <c r="G9" s="13">
+        <v>0.22130559540889527</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="32" customHeight="1">
       <c r="A10" s="5" t="s">
         <v>12</v>
       </c>
@@ -762,14 +981,23 @@
         <v>485</v>
       </c>
       <c r="C10" s="9">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="D10" s="8">
         <f t="shared" si="0"/>
-        <v>0.29896907216494845</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="32" customHeight="1">
+        <v>0.26391752577319588</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10">
+        <v>767</v>
+      </c>
+      <c r="G10" s="13">
+        <v>0.22059246476847857</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="32" customHeight="1">
       <c r="A11" s="6" t="s">
         <v>13</v>
       </c>
@@ -777,14 +1005,23 @@
         <v>988</v>
       </c>
       <c r="C11" s="7">
-        <v>294</v>
+        <v>240</v>
       </c>
       <c r="D11" s="8">
         <f t="shared" si="0"/>
-        <v>0.29757085020242913</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="32" customHeight="1">
+        <v>0.24291497975708501</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11">
+        <v>118</v>
+      </c>
+      <c r="G11" s="13">
+        <v>0.18322981366459629</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="32" customHeight="1">
       <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
@@ -792,14 +1029,23 @@
         <v>3719</v>
       </c>
       <c r="C12" s="9">
-        <v>1103</v>
+        <v>897</v>
       </c>
       <c r="D12" s="8">
         <f t="shared" si="0"/>
-        <v>0.29658510352245226</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="32" customHeight="1">
+        <v>0.2411938693197096</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12">
+        <v>328</v>
+      </c>
+      <c r="G12" s="13">
+        <v>0.24717407686510928</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="32" customHeight="1">
       <c r="A13" s="6" t="s">
         <v>15</v>
       </c>
@@ -807,14 +1053,23 @@
         <v>505</v>
       </c>
       <c r="C13" s="7">
-        <v>144</v>
+        <v>125</v>
       </c>
       <c r="D13" s="8">
         <f t="shared" si="0"/>
-        <v>0.28514851485148512</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="32" customHeight="1">
+        <v>0.24752475247524752</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13">
+        <v>128</v>
+      </c>
+      <c r="G13" s="13">
+        <v>0.26391752577319588</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="32" customHeight="1">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
@@ -822,14 +1077,23 @@
         <v>2788</v>
       </c>
       <c r="C14" s="9">
-        <v>790</v>
+        <v>617</v>
       </c>
       <c r="D14" s="8">
         <f t="shared" si="0"/>
-        <v>0.28335724533715928</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="32" customHeight="1">
+        <v>0.22130559540889527</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14">
+        <v>897</v>
+      </c>
+      <c r="G14" s="13">
+        <v>0.2411938693197096</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="32" customHeight="1">
       <c r="A15" s="6" t="s">
         <v>17</v>
       </c>
@@ -837,14 +1101,23 @@
         <v>3477</v>
       </c>
       <c r="C15" s="7">
-        <v>971</v>
+        <v>767</v>
       </c>
       <c r="D15" s="8">
         <f t="shared" si="0"/>
-        <v>0.27926373310324992</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="32" customHeight="1">
+        <v>0.22059246476847857</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F15">
+        <v>125</v>
+      </c>
+      <c r="G15" s="13">
+        <v>0.24752475247524752</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="32" customHeight="1">
       <c r="A16" s="5" t="s">
         <v>18</v>
       </c>
@@ -852,14 +1125,23 @@
         <v>769</v>
       </c>
       <c r="C16" s="9">
-        <v>213</v>
+        <v>166</v>
       </c>
       <c r="D16" s="8">
         <f t="shared" si="0"/>
-        <v>0.27698309492847856</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="32" customHeight="1">
+        <v>0.21586475942782835</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16">
+        <v>498</v>
+      </c>
+      <c r="G16" s="13">
+        <v>0.26447158789166225</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="32" customHeight="1">
       <c r="A17" s="6" t="s">
         <v>19</v>
       </c>
@@ -867,14 +1149,23 @@
         <v>2096</v>
       </c>
       <c r="C17" s="7">
-        <v>569</v>
+        <v>477</v>
       </c>
       <c r="D17" s="8">
         <f t="shared" si="0"/>
-        <v>0.27146946564885494</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="32" customHeight="1">
+        <v>0.22757633587786261</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F17">
+        <v>294</v>
+      </c>
+      <c r="G17" s="13">
+        <v>0.15441176470588236</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="32" customHeight="1">
       <c r="A18" s="5" t="s">
         <v>20</v>
       </c>
@@ -882,14 +1173,23 @@
         <v>1783</v>
       </c>
       <c r="C18" s="9">
-        <v>481</v>
+        <v>379</v>
       </c>
       <c r="D18" s="8">
         <f t="shared" si="0"/>
-        <v>0.26977005047672464</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="32" customHeight="1">
+        <v>0.21256309590577679</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="F18">
+        <v>1235</v>
+      </c>
+      <c r="G18" s="13">
+        <v>0.26231945624468989</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="32" customHeight="1">
       <c r="A19" s="6" t="s">
         <v>21</v>
       </c>
@@ -897,14 +1197,23 @@
         <v>756</v>
       </c>
       <c r="C19" s="7">
-        <v>200</v>
+        <v>155</v>
       </c>
       <c r="D19" s="8">
         <f t="shared" si="0"/>
-        <v>0.26455026455026454</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="32" customHeight="1">
+        <v>0.20502645502645503</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F19">
+        <v>229</v>
+      </c>
+      <c r="G19" s="13">
+        <v>0.20123022847100175</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="32" customHeight="1">
       <c r="A20" s="5" t="s">
         <v>22</v>
       </c>
@@ -912,14 +1221,23 @@
         <v>1138</v>
       </c>
       <c r="C20" s="9">
-        <v>274</v>
+        <v>229</v>
       </c>
       <c r="D20" s="8">
         <f t="shared" si="0"/>
-        <v>0.24077328646748683</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="32" customHeight="1">
+        <v>0.20123022847100175</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20">
+        <v>155</v>
+      </c>
+      <c r="G20" s="13">
+        <v>0.20502645502645503</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="32" customHeight="1">
       <c r="A21" s="6" t="s">
         <v>23</v>
       </c>
@@ -927,14 +1245,23 @@
         <v>644</v>
       </c>
       <c r="C21" s="7">
-        <v>151</v>
+        <v>118</v>
       </c>
       <c r="D21" s="8">
         <f t="shared" si="0"/>
-        <v>0.23447204968944099</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="32" customHeight="1">
+        <v>0.18322981366459629</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="F21">
+        <v>197</v>
+      </c>
+      <c r="G21" s="13">
+        <v>0.27437325905292481</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="32" customHeight="1">
       <c r="A22" s="5" t="s">
         <v>24</v>
       </c>
@@ -942,14 +1269,23 @@
         <v>687</v>
       </c>
       <c r="C22" s="9">
-        <v>158</v>
+        <v>124</v>
       </c>
       <c r="D22" s="8">
         <f t="shared" si="0"/>
-        <v>0.22998544395924309</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="32" customHeight="1">
+        <v>0.18049490538573509</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22">
+        <v>356</v>
+      </c>
+      <c r="G22" s="13">
+        <v>0.26253687315634217</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="32" customHeight="1">
       <c r="A23" s="6" t="s">
         <v>25</v>
       </c>
@@ -957,14 +1293,23 @@
         <v>1089</v>
       </c>
       <c r="C23" s="7">
-        <v>240</v>
+        <v>185</v>
       </c>
       <c r="D23" s="8">
         <f t="shared" si="0"/>
-        <v>0.22038567493112948</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="32" customHeight="1">
+        <v>0.16988062442607896</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="F23">
+        <v>166</v>
+      </c>
+      <c r="G23" s="13">
+        <v>0.21586475942782835</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="32" customHeight="1">
       <c r="A24" s="5" t="s">
         <v>26</v>
       </c>
@@ -972,14 +1317,23 @@
         <v>726</v>
       </c>
       <c r="C24" s="9">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="D24" s="8">
         <f t="shared" si="0"/>
-        <v>0.21349862258953167</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="32" customHeight="1">
+        <v>0.18870523415977961</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F24">
+        <v>185</v>
+      </c>
+      <c r="G24" s="13">
+        <v>0.16988062442607896</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="32" customHeight="1">
       <c r="A25" s="6" t="s">
         <v>27</v>
       </c>
@@ -987,15 +1341,36 @@
         <v>1904</v>
       </c>
       <c r="C25" s="7">
-        <v>368</v>
+        <v>294</v>
       </c>
       <c r="D25" s="8">
         <f t="shared" si="0"/>
-        <v>0.19327731092436976</v>
+        <v>0.15441176470588236</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25">
+        <v>382</v>
+      </c>
+      <c r="G25" s="13">
+        <v>0.26939351198871653</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="24">
+      <c r="E26" s="12" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="10" type="noConversion"/>
+  <conditionalFormatting sqref="G3:G25">
+    <cfRule type="top10" dxfId="4" priority="3" bottom="1" rank="5"/>
+    <cfRule type="aboveAverage" dxfId="3" priority="2" aboveAverage="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3:F25">
+    <cfRule type="aboveAverage" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>